--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="21929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BE61B30-D53D-426A-A018-9D1315CCAFC4}" xr6:coauthVersionLast="44" xr6:coauthVersionMax="44" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FABA608-37AC-4AFF-BA16-09C9F5F617BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="45">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -164,19 +164,29 @@
   </si>
   <si>
     <t>Application</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{users:Automation_SPI} </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="Consolas"/>
+      <family val="3"/>
     </font>
   </fonts>
   <fills count="2">
@@ -199,7 +209,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -207,6 +217,9 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -558,8 +571,8 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
+      <c r="C3" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">
@@ -630,8 +643,8 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>6</v>
+      <c r="C3" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FABA608-37AC-4AFF-BA16-09C9F5F617BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372419F7-6829-450A-957B-CBDC47E04CBE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="46">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -167,6 +167,9 @@
   </si>
   <si>
     <t xml:space="preserve">{users:Automation_SPI} </t>
+  </si>
+  <si>
+    <t>Debra Clements</t>
   </si>
 </sst>
 </file>
@@ -572,7 +575,7 @@
         <v>5</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.3">

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22325"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="22430"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{372419F7-6829-450A-957B-CBDC47E04CBE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56068974-39CF-490A-B4B3-956F226EB9A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
@@ -169,14 +169,14 @@
     <t xml:space="preserve">{users:Automation_SPI} </t>
   </si>
   <si>
-    <t>Debra Clements</t>
+    <t>SPI Automation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -190,6 +190,21 @@
       <color rgb="FF297BDE"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -209,10 +224,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
@@ -224,8 +240,10 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -574,7 +592,7 @@
       <c r="B3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>45</v>
       </c>
     </row>
@@ -601,8 +619,11 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="C3" r:id="rId1" tooltip="SPI Automation" display="https://lsc--qa--c.visualforce.com/0030r00000KHDtmAAH" xr:uid="{AE636F3D-F8AE-43CC-A92A-C8F49D6FBD83}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56068974-39CF-490A-B4B3-956F226EB9A1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01246C3E-AB73-4CF1-A7EA-15BA6630C1D0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25128"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\rei proj\product_automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFA28A7C-A080-4DB4-8B61-0BC273E5C760}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAF633A-8892-4F43-B275-05AC47F5B5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -133,40 +133,40 @@
     <t>Automation SPI3</t>
   </si>
   <si>
-    <t>fieldVisitDateandTime__c</t>
-  </si>
-  <si>
-    <t>fieldVisitEndDateTime__c</t>
-  </si>
-  <si>
-    <t>fieldDescription__c</t>
-  </si>
-  <si>
-    <t>fieldPointsdiscussedwithofficials__c</t>
-  </si>
-  <si>
-    <t>fieldSiteVisitPurpose__c</t>
-  </si>
-  <si>
-    <t>fieldSourceSiteVisit__c</t>
-  </si>
-  <si>
-    <t>fieldSupportingCommentsQuestion1__c</t>
-  </si>
-  <si>
-    <t>fieldTitle__c</t>
-  </si>
-  <si>
-    <t>fieldGranteePOCContact__c</t>
-  </si>
-  <si>
-    <t>fieldMonitoringType__c</t>
-  </si>
-  <si>
-    <t>fieldSiteVisitType__c</t>
-  </si>
-  <si>
     <t>Other</t>
+  </si>
+  <si>
+    <t>Title__c</t>
+  </si>
+  <si>
+    <t>GranteePOCContact__c</t>
+  </si>
+  <si>
+    <t>MonitoringType__c</t>
+  </si>
+  <si>
+    <t>SiteVisitType__c</t>
+  </si>
+  <si>
+    <t>VisitDateandTime__c</t>
+  </si>
+  <si>
+    <t>VisitEndDateTime__c</t>
+  </si>
+  <si>
+    <t>Description__c</t>
+  </si>
+  <si>
+    <t>Pointsdiscussedwithofficials__c</t>
+  </si>
+  <si>
+    <t>SiteVisitPurpose__c</t>
+  </si>
+  <si>
+    <t>SourceSiteVisit__c</t>
+  </si>
+  <si>
+    <t>SupportingCommentsQuestion1__c</t>
   </si>
 </sst>
 </file>
@@ -208,8 +208,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -533,64 +532,64 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>27</v>
       </c>
     </row>
@@ -603,67 +602,65 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2DDC02-74D6-4569-851C-F07FFE02569B}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="26.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="26.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>44</v>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -675,98 +672,98 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="C7" s="1" t="s">
+      <c r="B7" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C8" s="1" t="s">
+      <c r="B8" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C8" t="s">
         <v>6</v>
       </c>
     </row>
@@ -778,77 +775,76 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C7B991-153A-4254-A9EC-CB6E3111FFE0}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2" s="1">
+      <c r="B2" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="1">
+      <c r="B3" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3">
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="B4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="C4" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>5</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>36</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="B5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" t="s">
         <v>6</v>
       </c>
     </row>
@@ -860,25 +856,25 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.28515625" customWidth="1"/>
-    <col min="3" max="3" width="100.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.26953125" customWidth="1"/>
+    <col min="3" max="3" width="100.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -889,8 +885,8 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" t="s">
@@ -900,8 +896,8 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" t="s">
@@ -911,8 +907,8 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" t="s">
@@ -922,8 +918,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
         <v>3</v>
       </c>
       <c r="B6" t="s">
@@ -933,8 +929,8 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>3</v>
       </c>
       <c r="B7" t="s">
@@ -944,8 +940,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
         <v>3</v>
       </c>
       <c r="B8" t="s">
@@ -955,8 +951,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
         <v>3</v>
       </c>
       <c r="B9" t="s">
@@ -966,8 +962,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
         <v>3</v>
       </c>
       <c r="B10" t="s">
@@ -985,67 +981,65 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A304E392-7396-448A-86B5-CCFD1BE04B95}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>44</v>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1056,67 +1050,65 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02608AAB-67CB-461D-B36D-03C96B96BB37}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>44</v>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1127,66 +1119,64 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F18BA5-C512-4E65-B599-8A11292F0D8E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="8.7109375" style="1"/>
-    <col min="2" max="2" width="20.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16384" width="8.7109375" style="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="C2" s="1" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C3" s="1" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C3" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C4" s="1" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="1" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="C5" t="s">
         <v>27</v>
       </c>
     </row>

--- a/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
+++ b/src/main/resources/Organizational_SiteVisit_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\VA Org 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DAF633A-8892-4F43-B275-05AC47F5B5BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B7DFC80-5E9B-4D76-B21B-43F50BB94DAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" activeTab="7" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{9AB3C168-78A6-4CA6-B0EE-C4F246080D71}"/>
   </bookViews>
   <sheets>
     <sheet name="Creation" sheetId="1" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="46">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -167,6 +167,9 @@
   </si>
   <si>
     <t>SupportingCommentsQuestion1__c</t>
+  </si>
+  <si>
+    <t>Deshka Kostova</t>
   </si>
 </sst>
 </file>
@@ -235,9 +238,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -275,7 +278,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -381,7 +384,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -523,7 +526,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -532,13 +535,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27F20A35-8E6F-4015-873C-76781E4C62A4}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.453125" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -549,7 +552,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -560,7 +563,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -568,10 +571,10 @@
         <v>35</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -582,7 +585,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -602,13 +605,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A2DDC02-74D6-4569-851C-F07FFE02569B}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="26.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -619,7 +622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -630,7 +633,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -641,7 +644,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -652,7 +655,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -672,14 +675,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4969FD67-2E2F-4920-8A24-9B3F6A7CB976}">
   <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,7 +693,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -701,7 +704,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -712,7 +715,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -723,7 +726,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -734,7 +737,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -745,7 +748,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>5</v>
       </c>
@@ -756,7 +759,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>5</v>
       </c>
@@ -775,14 +778,14 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18C7B991-153A-4254-A9EC-CB6E3111FFE0}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="8.7265625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="30.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="41.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="8.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="30.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="41.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -793,7 +796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -804,7 +807,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -815,7 +818,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>5</v>
       </c>
@@ -826,7 +829,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -837,7 +840,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -856,14 +859,14 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31F8298A-0165-44BF-9061-10BEE0A93A27}">
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.26953125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.26953125" customWidth="1"/>
-    <col min="3" max="3" width="100.1796875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.21875" customWidth="1"/>
+    <col min="3" max="3" width="100.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -874,7 +877,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -885,7 +888,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -896,7 +899,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -907,7 +910,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -918,7 +921,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>3</v>
       </c>
@@ -929,7 +932,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>3</v>
       </c>
@@ -940,7 +943,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -951,7 +954,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>3</v>
       </c>
@@ -962,7 +965,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>3</v>
       </c>
@@ -981,13 +984,13 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A304E392-7396-448A-86B5-CCFD1BE04B95}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -998,7 +1001,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1009,7 +1012,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1020,7 +1023,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1031,7 +1034,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1050,13 +1053,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02608AAB-67CB-461D-B36D-03C96B96BB37}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1067,7 +1070,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1078,7 +1081,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1089,7 +1092,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1100,7 +1103,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
@@ -1119,13 +1122,13 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33F18BA5-C512-4E65-B599-8A11292F0D8E}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="8.77734375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="27.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="27.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1136,7 +1139,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -1147,7 +1150,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -1158,7 +1161,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -1169,7 +1172,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
